--- a/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2928" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="317">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,6 +316,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -339,6 +343,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -381,6 +388,12 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -461,8 +474,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-1
-</t>
+    <t>ele-1
+bdl-1</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -499,9 +512,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -522,6 +532,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -558,6 +578,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -565,6 +588,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -580,11 +606,8 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -633,6 +656,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -642,8 +668,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -699,8 +725,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -754,6 +780,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -781,8 +810,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1310,15 +1339,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1765,16 +1794,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1785,10 +1814,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1811,16 +1840,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1870,7 +1899,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1879,16 +1908,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1899,10 +1928,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1925,16 +1954,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1960,13 +1989,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1984,7 +2013,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1993,16 +2022,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2013,10 +2042,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2039,16 +2068,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2098,7 +2127,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2107,30 +2136,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2153,16 +2182,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2173,47 +2202,47 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AG8" t="s" s="2">
         <v>87</v>
       </c>
@@ -2221,30 +2250,30 @@
         <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2267,16 +2296,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2326,7 +2355,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2335,30 +2364,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2381,16 +2410,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2440,7 +2469,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2449,16 +2478,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2469,10 +2498,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2495,16 +2524,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2554,7 +2583,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2563,16 +2592,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2583,10 +2612,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2609,13 +2638,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2666,7 +2695,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2684,7 +2713,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2695,14 +2724,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2721,16 +2750,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2768,19 +2797,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2789,16 +2818,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2809,14 +2838,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2835,19 +2864,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2896,7 +2925,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2905,10 +2934,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -2925,10 +2954,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2951,15 +2980,17 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3008,7 +3039,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3017,16 +3048,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3037,10 +3068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3063,15 +3094,17 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3120,7 +3153,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3129,16 +3162,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3149,10 +3182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3175,13 +3208,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3220,17 +3253,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3239,16 +3272,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3259,10 +3292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3285,13 +3318,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3342,7 +3375,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3360,7 +3393,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3371,14 +3404,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3397,16 +3430,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3444,19 +3477,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3465,16 +3498,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3485,14 +3518,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3511,19 +3544,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3572,7 +3605,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3581,10 +3614,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3601,10 +3634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3630,10 +3663,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3684,7 +3717,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3696,7 +3729,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3713,10 +3746,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3739,16 +3772,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3798,7 +3831,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3807,16 +3840,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3827,10 +3860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3853,13 +3886,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3910,7 +3943,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3928,7 +3961,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3939,10 +3972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3965,13 +3998,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4022,7 +4055,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4031,16 +4064,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4051,10 +4084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4077,13 +4110,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4134,7 +4167,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4152,7 +4185,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4163,14 +4196,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4189,16 +4222,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4236,19 +4269,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4257,16 +4290,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4277,14 +4310,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4303,19 +4336,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4364,7 +4397,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4373,10 +4406,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4393,10 +4426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4419,16 +4452,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4454,13 +4487,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4478,7 +4511,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4487,16 +4520,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4507,10 +4540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4533,16 +4566,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4592,7 +4625,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4601,16 +4634,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4621,10 +4654,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4647,13 +4680,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4704,7 +4737,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4713,16 +4746,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4733,10 +4766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4759,13 +4792,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4816,7 +4849,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4834,7 +4867,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4845,14 +4878,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4871,16 +4904,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4918,19 +4951,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4939,16 +4972,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -4959,14 +4992,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4985,19 +5018,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5046,7 +5079,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5055,10 +5088,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5075,10 +5108,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5101,15 +5134,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5134,13 +5169,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5158,7 +5193,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5167,16 +5202,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5187,10 +5222,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5213,16 +5248,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5272,7 +5307,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5281,16 +5316,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5301,10 +5336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5327,15 +5362,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5384,7 +5421,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5393,16 +5430,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5413,10 +5450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5439,15 +5476,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5496,7 +5535,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5505,16 +5544,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5525,10 +5564,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5551,15 +5590,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5608,7 +5649,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5617,16 +5658,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5637,10 +5678,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5663,15 +5704,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5720,7 +5763,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5729,16 +5772,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5749,10 +5792,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5775,13 +5818,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5832,7 +5875,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5841,16 +5884,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5861,10 +5904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5887,13 +5930,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5944,7 +5987,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -5962,7 +6005,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -5973,14 +6016,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5999,16 +6042,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6046,19 +6089,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6067,16 +6110,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6087,14 +6130,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6113,19 +6156,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6174,7 +6217,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6183,10 +6226,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6203,10 +6246,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6229,15 +6272,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6286,7 +6331,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6295,16 +6340,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6315,10 +6360,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6341,15 +6386,17 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6398,7 +6445,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6407,16 +6454,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6427,10 +6474,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6453,16 +6500,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6512,7 +6559,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6521,16 +6568,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6541,10 +6588,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6567,16 +6614,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6626,7 +6673,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6635,16 +6682,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6655,10 +6702,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6681,16 +6728,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6740,7 +6787,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6758,7 +6805,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6769,13 +6816,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6797,13 +6844,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6854,7 +6901,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6863,16 +6910,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -6883,10 +6930,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6909,13 +6956,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6966,7 +7013,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -6984,7 +7031,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -6995,14 +7042,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7021,16 +7068,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7068,19 +7115,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7089,16 +7136,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7109,14 +7156,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7135,19 +7182,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7196,7 +7243,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7205,10 +7252,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7225,10 +7272,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7254,10 +7301,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7308,7 +7355,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7320,7 +7367,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7337,10 +7384,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7363,16 +7410,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7422,7 +7469,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7431,16 +7478,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7451,10 +7498,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7474,16 +7521,16 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7534,7 +7581,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7552,7 +7599,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7563,10 +7610,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7589,13 +7636,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7646,7 +7693,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7655,16 +7702,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7675,10 +7722,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7701,13 +7748,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7758,7 +7805,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7776,7 +7823,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7787,14 +7834,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7813,16 +7860,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7860,19 +7907,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7881,16 +7928,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -7901,14 +7948,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7927,19 +7974,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -7988,7 +8035,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -7997,10 +8044,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8017,10 +8064,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8043,16 +8090,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8078,13 +8125,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8102,7 +8149,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8111,16 +8158,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8131,10 +8178,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8157,16 +8204,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8216,7 +8263,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8225,16 +8272,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8245,10 +8292,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8271,13 +8318,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8328,7 +8375,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8337,16 +8384,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8357,10 +8404,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8383,13 +8430,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8440,7 +8487,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8458,7 +8505,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8469,14 +8516,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8495,16 +8542,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8542,19 +8589,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8563,16 +8610,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8583,14 +8630,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8609,19 +8656,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8670,7 +8717,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8679,10 +8726,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8699,10 +8746,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8725,15 +8772,17 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8758,13 +8807,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8782,7 +8831,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8791,16 +8840,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8811,10 +8860,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8837,16 +8886,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8896,7 +8945,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -8905,16 +8954,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -8925,10 +8974,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8951,15 +9000,17 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9008,7 +9059,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9017,16 +9068,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9037,10 +9088,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9063,15 +9114,17 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9120,7 +9173,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9129,16 +9182,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9149,10 +9202,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9175,15 +9228,17 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9232,7 +9287,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9241,16 +9296,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9261,10 +9316,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9287,15 +9342,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9344,7 +9401,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9353,16 +9410,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9373,10 +9430,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9399,13 +9456,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9456,7 +9513,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9465,16 +9522,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9485,10 +9542,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9511,13 +9568,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9568,7 +9625,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9586,7 +9643,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9597,14 +9654,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9623,16 +9680,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9670,19 +9727,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9691,16 +9748,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9711,14 +9768,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9737,19 +9794,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9798,7 +9855,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9807,10 +9864,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9827,10 +9884,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9853,15 +9910,17 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -9910,7 +9969,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -9919,16 +9978,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -9939,10 +9998,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9965,15 +10024,17 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10022,7 +10083,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10031,16 +10092,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10051,10 +10112,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10077,16 +10138,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10136,7 +10197,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10145,16 +10206,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10165,10 +10226,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10191,16 +10252,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10250,7 +10311,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10259,16 +10320,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10279,10 +10340,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10305,16 +10366,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10364,7 +10425,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10382,7 +10443,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10393,10 +10454,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10419,19 +10480,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10480,7 +10541,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10489,16 +10550,16 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2928" uniqueCount="308">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,10 +316,6 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -343,9 +339,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -388,12 +381,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -474,8 +461,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-1</t>
+    <t xml:space="preserve">bdl-1
+</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -512,6 +499,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -532,16 +522,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -578,9 +558,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -588,9 +565,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -606,8 +580,11 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>open</t>
+  </si>
+  <si>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -656,9 +633,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -668,8 +642,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -725,8 +699,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -780,9 +754,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -810,8 +781,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1339,15 +1310,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1794,16 +1765,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1814,10 +1785,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1840,16 +1811,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1899,7 +1870,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1908,16 +1879,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1928,10 +1899,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1954,16 +1925,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1989,32 +1960,32 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2022,16 +1993,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2042,10 +2013,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2068,16 +2039,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2127,7 +2098,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2136,30 +2107,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2182,16 +2153,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2202,78 +2173,78 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2296,16 +2267,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2355,7 +2326,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2364,30 +2335,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2410,16 +2381,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2469,7 +2440,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2478,16 +2449,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2498,10 +2469,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2524,16 +2495,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2583,7 +2554,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2592,16 +2563,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2612,10 +2583,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2638,13 +2609,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2695,7 +2666,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2713,7 +2684,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2724,14 +2695,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2750,16 +2721,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2797,19 +2768,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2818,16 +2789,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2838,14 +2809,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2864,19 +2835,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2925,7 +2896,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2934,10 +2905,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -2954,10 +2925,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2980,17 +2951,15 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3039,7 +3008,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3048,16 +3017,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3068,10 +3037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3094,17 +3063,15 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3153,7 +3120,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3162,16 +3129,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3182,10 +3149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3208,13 +3175,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3253,17 +3220,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3272,16 +3239,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3292,10 +3259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3318,13 +3285,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3375,7 +3342,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3393,7 +3360,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3404,14 +3371,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3430,16 +3397,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3477,19 +3444,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3498,16 +3465,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3518,14 +3485,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3544,19 +3511,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O20" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3605,7 +3572,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3614,10 +3581,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3634,10 +3601,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3663,10 +3630,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3717,7 +3684,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3729,7 +3696,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3746,10 +3713,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3772,16 +3739,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3831,7 +3798,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3840,16 +3807,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3860,10 +3827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3886,13 +3853,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3943,7 +3910,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3961,7 +3928,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3972,10 +3939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3998,13 +3965,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4055,7 +4022,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4064,16 +4031,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4084,10 +4051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4110,13 +4077,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4167,7 +4134,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4185,7 +4152,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4196,14 +4163,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4222,16 +4189,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4269,19 +4236,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4290,16 +4257,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4310,14 +4277,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4336,19 +4303,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4397,7 +4364,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4406,10 +4373,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4426,10 +4393,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4452,16 +4419,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4487,13 +4454,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4511,7 +4478,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4520,16 +4487,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4540,10 +4507,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4566,16 +4533,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4625,7 +4592,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4634,16 +4601,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4654,10 +4621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4680,13 +4647,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4737,7 +4704,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4746,16 +4713,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4766,10 +4733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4792,13 +4759,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4849,7 +4816,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4867,7 +4834,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4878,14 +4845,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4904,16 +4871,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4951,19 +4918,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4972,16 +4939,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -4992,14 +4959,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5018,19 +4985,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5079,7 +5046,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5088,10 +5055,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5108,10 +5075,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5134,17 +5101,15 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5169,13 +5134,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5193,7 +5158,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5202,16 +5167,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5222,10 +5187,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5248,16 +5213,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5307,7 +5272,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5316,16 +5281,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5336,10 +5301,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5362,17 +5327,15 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5421,7 +5384,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5430,16 +5393,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5450,10 +5413,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5476,17 +5439,15 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5535,7 +5496,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5544,16 +5505,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5564,10 +5525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5590,17 +5551,15 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5649,7 +5608,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5658,16 +5617,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5678,10 +5637,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5704,17 +5663,15 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5763,7 +5720,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5772,16 +5729,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5792,10 +5749,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5818,13 +5775,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5875,7 +5832,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5884,16 +5841,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5904,10 +5861,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5930,13 +5887,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5987,7 +5944,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6005,7 +5962,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6016,14 +5973,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6042,16 +5999,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6089,19 +6046,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6110,16 +6067,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6130,14 +6087,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6156,19 +6113,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O43" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6217,7 +6174,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6226,10 +6183,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6246,10 +6203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6272,17 +6229,15 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6331,7 +6286,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6340,16 +6295,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6360,10 +6315,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6386,17 +6341,15 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6445,7 +6398,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6454,16 +6407,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6474,10 +6427,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6500,16 +6453,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6559,7 +6512,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6568,16 +6521,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6588,10 +6541,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6614,16 +6567,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6673,7 +6626,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6682,16 +6635,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6702,10 +6655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6728,16 +6681,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6787,7 +6740,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6805,7 +6758,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6816,13 +6769,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6844,13 +6797,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6901,7 +6854,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6910,16 +6863,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -6930,10 +6883,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6956,13 +6909,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7013,7 +6966,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7031,7 +6984,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7042,14 +6995,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7068,16 +7021,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7115,19 +7068,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7136,16 +7089,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7156,14 +7109,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7182,19 +7135,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7243,7 +7196,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7252,10 +7205,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7272,10 +7225,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7301,10 +7254,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7355,7 +7308,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7367,7 +7320,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7384,10 +7337,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7410,16 +7363,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7469,7 +7422,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7478,16 +7431,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7498,10 +7451,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7521,16 +7474,16 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7581,7 +7534,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7599,7 +7552,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7610,10 +7563,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7636,13 +7589,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7693,7 +7646,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7702,16 +7655,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7722,10 +7675,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7748,13 +7701,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7805,7 +7758,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7823,7 +7776,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7834,14 +7787,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7860,16 +7813,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7907,19 +7860,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7928,16 +7881,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -7948,14 +7901,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7974,19 +7927,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8035,7 +7988,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8044,10 +7997,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8064,10 +8017,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8090,16 +8043,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8125,13 +8078,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8149,7 +8102,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8158,16 +8111,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8178,10 +8131,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8204,16 +8157,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8263,7 +8216,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8272,16 +8225,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8292,10 +8245,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8318,13 +8271,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8375,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8384,16 +8337,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8404,10 +8357,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8430,13 +8383,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8487,7 +8440,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8505,7 +8458,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8516,14 +8469,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8542,16 +8495,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8589,19 +8542,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8610,16 +8563,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8630,14 +8583,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8656,19 +8609,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8717,7 +8670,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8726,10 +8679,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8746,10 +8699,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8772,17 +8725,15 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8807,13 +8758,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8831,7 +8782,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8840,16 +8791,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8860,10 +8811,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8886,16 +8837,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8945,7 +8896,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -8954,16 +8905,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -8974,10 +8925,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9000,17 +8951,15 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9059,7 +9008,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9068,16 +9017,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9088,10 +9037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9114,17 +9063,15 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9173,7 +9120,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9182,16 +9129,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9202,10 +9149,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9228,17 +9175,15 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9287,7 +9232,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9296,16 +9241,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9316,10 +9261,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9342,17 +9287,15 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9401,7 +9344,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9410,16 +9353,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ71" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9430,10 +9373,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9456,13 +9399,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9513,7 +9456,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9522,16 +9465,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9542,10 +9485,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9568,13 +9511,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9625,7 +9568,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9643,7 +9586,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9654,14 +9597,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9680,16 +9623,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9727,19 +9670,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9748,16 +9691,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9768,14 +9711,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9794,19 +9737,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9855,7 +9798,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9864,10 +9807,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9884,10 +9827,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9910,17 +9853,15 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -9969,7 +9910,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -9978,16 +9919,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ76" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -9998,10 +9939,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10024,17 +9965,15 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10083,7 +10022,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10092,16 +10031,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10112,10 +10051,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10138,16 +10077,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10197,7 +10136,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10206,16 +10145,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ78" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10226,10 +10165,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10252,16 +10191,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10311,7 +10250,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10320,16 +10259,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ79" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10340,10 +10279,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10366,16 +10305,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10425,7 +10364,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10443,7 +10382,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10454,10 +10393,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10480,19 +10419,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10541,7 +10480,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10550,16 +10489,16 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ81" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundledelivery.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2928" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="317">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,6 +316,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -339,6 +343,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -381,6 +388,12 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -461,8 +474,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-1
-</t>
+    <t>ele-1
+bdl-1</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -499,9 +512,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -522,6 +532,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -558,6 +578,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -565,6 +588,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -580,11 +606,8 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -633,6 +656,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -642,8 +668,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -699,8 +725,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -754,6 +780,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -781,8 +810,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1310,15 +1339,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1765,16 +1794,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1785,10 +1814,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1811,16 +1840,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1870,7 +1899,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1879,16 +1908,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1899,10 +1928,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1925,16 +1954,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1960,13 +1989,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1984,7 +2013,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1993,16 +2022,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2013,10 +2042,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2039,16 +2068,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2098,7 +2127,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2107,30 +2136,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2153,16 +2182,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2173,47 +2202,47 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AG8" t="s" s="2">
         <v>87</v>
       </c>
@@ -2221,30 +2250,30 @@
         <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2267,16 +2296,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2326,7 +2355,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2335,30 +2364,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2381,16 +2410,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2440,7 +2469,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2449,16 +2478,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2469,10 +2498,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2495,16 +2524,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2554,7 +2583,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2563,16 +2592,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2583,10 +2612,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2609,13 +2638,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2666,7 +2695,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2684,7 +2713,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2695,14 +2724,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2721,16 +2750,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2768,19 +2797,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2789,16 +2818,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2809,14 +2838,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2835,19 +2864,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2896,7 +2925,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2905,10 +2934,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -2925,10 +2954,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2951,15 +2980,17 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3008,7 +3039,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3017,16 +3048,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3037,10 +3068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3063,15 +3094,17 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3120,7 +3153,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3129,16 +3162,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3149,10 +3182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3175,13 +3208,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3220,17 +3253,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3239,16 +3272,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3259,10 +3292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3285,13 +3318,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3342,7 +3375,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3360,7 +3393,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3371,14 +3404,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3397,16 +3430,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3444,19 +3477,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3465,16 +3498,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3485,14 +3518,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3511,19 +3544,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3572,7 +3605,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3581,10 +3614,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3601,10 +3634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3630,10 +3663,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3684,7 +3717,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3696,7 +3729,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3713,10 +3746,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3739,16 +3772,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3798,7 +3831,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3807,16 +3840,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3827,10 +3860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3853,13 +3886,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3910,7 +3943,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3928,7 +3961,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3939,10 +3972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3965,13 +3998,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4022,7 +4055,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4031,16 +4064,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4051,10 +4084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4077,13 +4110,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4134,7 +4167,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4152,7 +4185,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4163,14 +4196,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4189,16 +4222,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4236,19 +4269,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4257,16 +4290,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4277,14 +4310,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4303,19 +4336,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4364,7 +4397,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4373,10 +4406,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4393,10 +4426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4419,16 +4452,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4454,13 +4487,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4478,7 +4511,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4487,16 +4520,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4507,10 +4540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4533,16 +4566,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4592,7 +4625,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4601,16 +4634,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4621,10 +4654,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4647,13 +4680,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4704,7 +4737,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4713,16 +4746,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4733,10 +4766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4759,13 +4792,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4816,7 +4849,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4834,7 +4867,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4845,14 +4878,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4871,16 +4904,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4918,19 +4951,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4939,16 +4972,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -4959,14 +4992,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4985,19 +5018,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5046,7 +5079,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5055,10 +5088,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5075,10 +5108,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5101,15 +5134,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5134,13 +5169,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5158,7 +5193,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5167,16 +5202,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5187,10 +5222,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5213,16 +5248,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5272,7 +5307,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5281,16 +5316,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5301,10 +5336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5327,15 +5362,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5384,7 +5421,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5393,16 +5430,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5413,10 +5450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5439,15 +5476,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5496,7 +5535,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5505,16 +5544,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5525,10 +5564,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5551,15 +5590,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5608,7 +5649,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5617,16 +5658,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5637,10 +5678,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5663,15 +5704,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5720,7 +5763,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5729,16 +5772,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5749,10 +5792,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5775,13 +5818,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5832,7 +5875,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5841,16 +5884,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5861,10 +5904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5887,13 +5930,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5944,7 +5987,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -5962,7 +6005,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -5973,14 +6016,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5999,16 +6042,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6046,19 +6089,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6067,16 +6110,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6087,14 +6130,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6113,19 +6156,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6174,7 +6217,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6183,10 +6226,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6203,10 +6246,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6229,15 +6272,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6286,7 +6331,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6295,16 +6340,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6315,10 +6360,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6341,15 +6386,17 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6398,7 +6445,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6407,16 +6454,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6427,10 +6474,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6453,16 +6500,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6512,7 +6559,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6521,16 +6568,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6541,10 +6588,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6567,16 +6614,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6626,7 +6673,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6635,16 +6682,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6655,10 +6702,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6681,16 +6728,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6740,7 +6787,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6758,7 +6805,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6769,13 +6816,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6797,13 +6844,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6854,7 +6901,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6863,16 +6910,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -6883,10 +6930,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6909,13 +6956,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6966,7 +7013,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -6984,7 +7031,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -6995,14 +7042,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7021,16 +7068,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7068,19 +7115,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7089,16 +7136,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7109,14 +7156,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7135,19 +7182,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7196,7 +7243,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7205,10 +7252,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7225,10 +7272,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7254,10 +7301,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7308,7 +7355,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7320,7 +7367,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7337,10 +7384,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7363,16 +7410,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7422,7 +7469,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7431,16 +7478,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7451,10 +7498,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7474,16 +7521,16 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7534,7 +7581,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7552,7 +7599,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7563,10 +7610,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7589,13 +7636,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7646,7 +7693,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7655,16 +7702,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7675,10 +7722,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7701,13 +7748,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7758,7 +7805,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7776,7 +7823,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7787,14 +7834,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7813,16 +7860,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7860,19 +7907,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7881,16 +7928,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -7901,14 +7948,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7927,19 +7974,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -7988,7 +8035,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -7997,10 +8044,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8017,10 +8064,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8043,16 +8090,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8078,13 +8125,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8102,7 +8149,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8111,16 +8158,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8131,10 +8178,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8157,16 +8204,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8216,7 +8263,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8225,16 +8272,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8245,10 +8292,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8271,13 +8318,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8328,7 +8375,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8337,16 +8384,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8357,10 +8404,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8383,13 +8430,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8440,7 +8487,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8458,7 +8505,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8469,14 +8516,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8495,16 +8542,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8542,19 +8589,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8563,16 +8610,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8583,14 +8630,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8609,19 +8656,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8670,7 +8717,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8679,10 +8726,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8699,10 +8746,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8725,15 +8772,17 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8758,13 +8807,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8782,7 +8831,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8791,16 +8840,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8811,10 +8860,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8837,16 +8886,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8896,7 +8945,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -8905,16 +8954,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -8925,10 +8974,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8951,15 +9000,17 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9008,7 +9059,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9017,16 +9068,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9037,10 +9088,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9063,15 +9114,17 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9120,7 +9173,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9129,16 +9182,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9149,10 +9202,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9175,15 +9228,17 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9232,7 +9287,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9241,16 +9296,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9261,10 +9316,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9287,15 +9342,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9344,7 +9401,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9353,16 +9410,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9373,10 +9430,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9399,13 +9456,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9456,7 +9513,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9465,16 +9522,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9485,10 +9542,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9511,13 +9568,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9568,7 +9625,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9586,7 +9643,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9597,14 +9654,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9623,16 +9680,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9670,19 +9727,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9691,16 +9748,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9711,14 +9768,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9737,19 +9794,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9798,7 +9855,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9807,10 +9864,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9827,10 +9884,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9853,15 +9910,17 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -9910,7 +9969,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -9919,16 +9978,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -9939,10 +9998,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9965,15 +10024,17 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10022,7 +10083,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10031,16 +10092,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10051,10 +10112,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10077,16 +10138,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10136,7 +10197,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10145,16 +10206,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10165,10 +10226,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10191,16 +10252,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10250,7 +10311,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10259,16 +10320,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10279,10 +10340,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10305,16 +10366,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10364,7 +10425,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10382,7 +10443,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10393,10 +10454,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10419,19 +10480,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10480,7 +10541,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10489,16 +10550,16 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
